--- a/result/LOOCV/SVR/without_41/nBA/1&2_nBA_SVR_LOOCV_mechanism_oriented_perc=10_without_41.xlsx
+++ b/result/LOOCV/SVR/without_41/nBA/1&2_nBA_SVR_LOOCV_mechanism_oriented_perc=10_without_41.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9998092656650539</v>
+        <v>0.9997091611488841</v>
       </c>
       <c r="C2" t="n">
-        <v>2.010088906943827</v>
+        <v>2.045045074037789</v>
       </c>
       <c r="D2" t="n">
         <v>2.45</v>
@@ -468,10 +468,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.998833185915031</v>
+        <v>0.9813831468025906</v>
       </c>
       <c r="C3" t="n">
-        <v>2.186750969178623</v>
+        <v>1.792346027754115</v>
       </c>
       <c r="D3" t="n">
         <v>1.8</v>
@@ -500,10 +500,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9850927891069954</v>
+        <v>0.9794488686002217</v>
       </c>
       <c r="C5" t="n">
-        <v>1.926708454769777</v>
+        <v>1.883596874421549</v>
       </c>
       <c r="D5" t="n">
         <v>1.9</v>
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9814349336664333</v>
+        <v>0.9865994338081936</v>
       </c>
       <c r="C7" t="n">
-        <v>1.487159030548405</v>
+        <v>1.491500005529407</v>
       </c>
       <c r="D7" t="n">
         <v>1.44</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9999964048088655</v>
+        <v>0.9996280029853266</v>
       </c>
       <c r="C10" t="n">
-        <v>1.670085893441132</v>
+        <v>1.697038304773917</v>
       </c>
       <c r="D10" t="n">
         <v>1.75</v>
@@ -599,7 +599,7 @@
         <v>0.9587316371127561</v>
       </c>
       <c r="C11" t="n">
-        <v>3.381899475583814</v>
+        <v>3.381899475583812</v>
       </c>
       <c r="D11" t="n">
         <v>3.81</v>
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9716094357710331</v>
+        <v>0.9716094357710326</v>
       </c>
       <c r="C12" t="n">
         <v>1.332607326384635</v>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9735840151243158</v>
+        <v>0.9735840151243157</v>
       </c>
       <c r="C14" t="n">
         <v>1.483277223111315</v>
@@ -692,10 +692,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8022107316016946</v>
+        <v>0.9772256612384058</v>
       </c>
       <c r="C17" t="n">
-        <v>2.902319279323278</v>
+        <v>2.650538110962468</v>
       </c>
       <c r="D17" t="n">
         <v>2.8</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.974009868174144</v>
+        <v>0.9740098681741444</v>
       </c>
       <c r="C18" t="n">
         <v>2.223919059298127</v>
@@ -727,7 +727,7 @@
         <v>0.9789205198851212</v>
       </c>
       <c r="C19" t="n">
-        <v>1.669245618660062</v>
+        <v>1.669245618660061</v>
       </c>
       <c r="D19" t="n">
         <v>1.7</v>
